--- a/output/full_scan/batch_seq6_2026-10-12.xlsx
+++ b/output/full_scan/batch_seq6_2026-10-12.xlsx
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6187</v>
+        <v>6278</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>960.8408247462484</v>
+        <v>1211.799533131937</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1675</v>
+        <v>272.5</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,49 +552,49 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>75.81046892818505</v>
+        <v>82.00878724677798</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>28.07080915508585</v>
+        <v>37.27556256605359</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1.819415927638736</v>
+        <v>2.137482293646104</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>38.22914826198532</v>
+        <v>5.680362317311932</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6185</v>
+        <v>6187</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>幃翔</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>937.9526277041172</v>
+        <v>1160.840824746248</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>13.5</v>
+        <v>1675</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,29 +605,29 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>66.27915338817618</v>
+        <v>75.81046887922281</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>20.42174219568371</v>
+        <v>28.07080909008199</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>3.085769100576581</v>
+        <v>1.819415927638736</v>
       </c>
       <c r="K3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="L3" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.0923193980963275</v>
+        <v>38.22914826583082</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, williams_r_recovery, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>919</v>
+        <v>1154</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>174</v>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>73.33463706819306</v>
+        <v>73.33463684859183</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>34.8350543247852</v>
+        <v>34.83505432080556</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>5.682550530895629</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>1.379261408662419</v>
+        <v>1.379261408061554</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6282</v>
+        <v>6185</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>幃翔</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>908.941661681476</v>
+        <v>1107.952627704117</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>45.7</v>
+        <v>13.5</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>59.00722664692948</v>
+        <v>66.27915322763079</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>16.70333822149325</v>
+        <v>20.42174219568371</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>4.731666091975979</v>
+        <v>3.085769100576581</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.3470197935311314</v>
+        <v>0.0923193981564133</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, williams_r_recovery, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6210</v>
+        <v>6197</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>慶生</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>897.8232270663082</v>
+        <v>1103.101443868276</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>19.6</v>
+        <v>390.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>56.36975066216293</v>
+        <v>81.2918243136111</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>4.065470758977333</v>
+        <v>29.17696635007971</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>6.896969370727243</v>
+        <v>1.910144386827581</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1545324966763408</v>
+        <v>7.615624875570239</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6470</v>
+        <v>6285</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>宇智</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>874.8504514657296</v>
+        <v>1084.65274761286</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>45.8</v>
+        <v>263.5</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,49 +817,49 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>78.14597722723822</v>
+        <v>68.29381432143846</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>21.9919538640651</v>
+        <v>21.89832019215843</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>6.537532860309691</v>
+        <v>2.065274761285976</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.2006501174848995</v>
+        <v>3.822827887159828</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6217</v>
+        <v>6271</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>中探針</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>821.9570234170899</v>
+        <v>1079.96770801918</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>179.5</v>
+        <v>247.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,49 +870,49 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>55.03220659939838</v>
+        <v>70.32992079384385</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>13.92240114796732</v>
+        <v>30.106748970612</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>2.550744593886538</v>
+        <v>1.297712517705838</v>
       </c>
       <c r="K8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="L8" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M8" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.3183738267879256</v>
+        <v>1.141785864062656</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6278</v>
+        <v>6210</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>慶生</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>806.7995331319371</v>
+        <v>1067.823227066308</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>272.5</v>
+        <v>19.6</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>82.00878723277016</v>
+        <v>56.36975064421495</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>37.27556252764863</v>
+        <v>4.065470721151375</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.137482293646104</v>
+        <v>6.896969370727243</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>5.680362317792598</v>
+        <v>0.1545324967244088</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6234</v>
+        <v>6277</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>高僑</t>
+          <t>宏正</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>801.9145686977694</v>
+        <v>1060.787631364843</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>43.45</v>
+        <v>81.3</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>63.06396862498909</v>
+        <v>63.03276287289819</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>24.19933383065792</v>
+        <v>15.85481095655647</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.970830385955089</v>
+        <v>2.537994170572113</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.4057254071332883</v>
+        <v>0.3874073862329079</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6285</v>
+        <v>6191</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>799.6527476128598</v>
+        <v>1059</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>263.5</v>
+        <v>93.5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>68.29381425844444</v>
+        <v>76.81614412906876</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>21.89832011004541</v>
+        <v>23.05988237318663</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2.065274761285976</v>
+        <v>5.864384918678307</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>3.822827888001057</v>
+        <v>1.02706929065969</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6197</v>
+        <v>6470</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>宇智</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>793.1014438682759</v>
+        <v>1044.850451465731</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>390.5</v>
+        <v>45.8</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>81.29182436831768</v>
+        <v>78.1459773519164</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>29.17696638827644</v>
+        <v>21.99195386800011</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.910144386827581</v>
+        <v>6.537532860309691</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>7.615624875810608</v>
+        <v>0.2006501172445543</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6191</v>
+        <v>6282</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>779</v>
+        <v>1023.941661681472</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>93.5</v>
+        <v>45.7</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>76.81614424563789</v>
+        <v>59.00722663679709</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>23.05988240089775</v>
+        <v>16.70333834839118</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>5.864384918678307</v>
+        <v>4.731666091975979</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>1.027069291260562</v>
+        <v>0.3470197933628794</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6292</v>
+        <v>6225</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>迅德</t>
+          <t>天瀚</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>764.9988665830756</v>
+        <v>1005.363839712118</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>69.3</v>
+        <v>78.7</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>58.82769342211995</v>
+        <v>69.20489809187043</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>35.0862637378676</v>
+        <v>23.85315306139308</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.969764113059612</v>
+        <v>1.507690192315699</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-0.0580874099300612</v>
+        <v>1.250552431113461</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6245</v>
+        <v>6257</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>立端</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>764.747742065145</v>
+        <v>972.7823959035248</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>87.5</v>
+        <v>287</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,49 +1241,49 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>55.92379908256479</v>
+        <v>73.78034399165333</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>32.31174722975346</v>
+        <v>36.24367754897411</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.8679182513210498</v>
+        <v>1.121413917294559</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.0261021475127185</v>
+        <v>4.164019175106184</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6223</v>
+        <v>6214</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>764.0224554286143</v>
+        <v>972.2949289676344</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>6130</v>
+        <v>193</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,49 +1294,49 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>61.50810878166953</v>
+        <v>69.93755588706904</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>12.62472540423208</v>
+        <v>25.86644936649643</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.382402340662262</v>
+        <v>0.8410114262911069</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>69.43285630857562</v>
+        <v>-0.8278529743902485</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, obv_uptrend, invest_trust_buy_2d, bb_squeeze_breakout, cci_momentum</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, cci_momentum, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6271</v>
+        <v>6234</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>高僑</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>749.9677080191803</v>
+        <v>971.9145686977658</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>247.5</v>
+        <v>43.45</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>70.32992079384385</v>
+        <v>63.06396860493156</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>30.10674888851627</v>
+        <v>24.19933384973955</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.297712517705838</v>
+        <v>1.970830385955089</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>1.141785864303014</v>
+        <v>0.4057254068929403</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6277</v>
+        <v>6223</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>宏正</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>735.7876313648433</v>
+        <v>964.0224554286144</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>81.3</v>
+        <v>6130</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,49 +1400,49 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>63.03276289072519</v>
+        <v>61.50810874816975</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>15.85481090313</v>
+        <v>12.62472540043959</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>2.537994170572113</v>
+        <v>1.382402340662262</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.3874073862809813</v>
+        <v>69.43285630136489</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, invest_trust_buy_2d, bb_squeeze_breakout, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6188</v>
+        <v>6274</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>廣明</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>714.4936235671103</v>
+        <v>876.0451155248124</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>65.7</v>
+        <v>1735</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,49 +1453,49 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>59.97695362636792</v>
+        <v>67.0384019906878</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>25.53037355857673</v>
+        <v>25.18395228120022</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>3.891042703700818</v>
+        <v>0.4411771512135932</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.5475597532745544</v>
+        <v>31.98552043839558</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6261</v>
+        <v>6196</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>久元</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>709</v>
+        <v>869.4620654083438</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>84</v>
+        <v>657</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,49 +1506,49 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>64.02671231588167</v>
+        <v>69.08420697094373</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>11.5178578991175</v>
+        <v>37.07741840062484</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>5.164435463751119</v>
+        <v>1.033563799544327</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.4001381580406555</v>
+        <v>11.17138561609953</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6192</v>
+        <v>6188</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>巨路</t>
+          <t>廣明</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>707.4852817614676</v>
+        <v>854.4936235671063</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>114</v>
+        <v>65.7</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>58.89709563138392</v>
+        <v>59.97695327522725</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>27.49383325930642</v>
+        <v>25.53037366456037</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2.828722647038941</v>
+        <v>3.891042703700818</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.5083594754938945</v>
+        <v>0.5475597526736826</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6274</v>
+        <v>6261</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>久元</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>706.0451155248123</v>
+        <v>849</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1735</v>
+        <v>84</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,49 +1612,49 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>67.03840200948551</v>
+        <v>64.02671231049121</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>25.18395235577465</v>
+        <v>11.5178578655924</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.4411771512135932</v>
+        <v>5.164435463751119</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>31.98552044091914</v>
+        <v>0.4001381579925908</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6170</v>
+        <v>6192</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>統振</t>
+          <t>巨路</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>702.5933745928497</v>
+        <v>847.485281761467</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>49.5</v>
+        <v>114</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>62.49525460387563</v>
+        <v>58.89709543181006</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>22.14025783335968</v>
+        <v>27.49383322535351</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.228240082006089</v>
+        <v>2.828722647038941</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.1034526724439336</v>
+        <v>0.5083594756140832</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6225</v>
+        <v>6217</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>天瀚</t>
+          <t>中探針</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>695.3638397121181</v>
+        <v>821.9570234170892</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>78.7</v>
+        <v>179.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>69.20489805790874</v>
+        <v>55.03220657644685</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>23.8531529345742</v>
+        <v>13.92240112144807</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.507690192315699</v>
+        <v>2.550744593886538</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>1.250552431317755</v>
+        <v>0.3183738270643215</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6201</v>
+        <v>6416</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>亞弘電</t>
+          <t>瑞祺電通</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>691.5384502631779</v>
+        <v>808.5096585668114</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>45.95</v>
+        <v>120</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>60.1695422908169</v>
+        <v>59.88094409859049</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>29.31514441785161</v>
+        <v>34.4378871783921</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>4.599124089200177</v>
+        <v>0.4524124260061413</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.103434014440973</v>
+        <v>-0.3700567832313641</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend, cci_momentum</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6257</v>
+        <v>6201</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>亞弘電</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>687.7823959035248</v>
+        <v>806.5384502631779</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>287</v>
+        <v>45.95</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>73.78034401676382</v>
+        <v>60.16954232480177</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>36.24367755991202</v>
+        <v>29.31514433162762</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.121413917294559</v>
+        <v>4.599124089200177</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>4.164019175226358</v>
+        <v>0.103434014368868</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6168</v>
+        <v>6174</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>宏齊</t>
+          <t>安碁</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>685.5746933678303</v>
+        <v>806.3459815560723</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>39</v>
+        <v>61.1</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>52.47142058050103</v>
+        <v>67.29823082533591</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>50.08428717612443</v>
+        <v>26.42163664575091</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.5560884894851494</v>
+        <v>2.81367713002037</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,11 +1895,11 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.7047583215047748</v>
+        <v>1.845493992536975</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1916,7 +1916,7 @@
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>678.274611394368</v>
+        <v>793.274611394368</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>112.5</v>
@@ -1930,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>65.01792236347853</v>
+        <v>65.01792235532855</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>31.59677836924732</v>
+        <v>31.59677835562961</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>0.9274611394367984</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.5097986326799928</v>
+        <v>0.5097986325838475</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6205</v>
+        <v>6456</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>詮欣</t>
+          <t>GIS-KY</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>673.7986580112243</v>
+        <v>775.540648217016</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>70.59999999999999</v>
+        <v>102</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>55.43677589650424</v>
+        <v>74.82551481627979</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>32.24196190785737</v>
+        <v>40.02545725532599</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.2314463443453805</v>
+        <v>1.354064821701602</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.07845814749775649</v>
+        <v>2.37259097993782</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6416</v>
+        <v>6209</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>瑞祺電通</t>
+          <t>今國光</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>673.5096585668114</v>
+        <v>769.1619990532332</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>120</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>59.8809441887915</v>
+        <v>65.14338000714449</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>34.43788719660134</v>
+        <v>38.05898584509965</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.4524124260061413</v>
+        <v>2.321554534122129</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.3700567833274952</v>
+        <v>0.8651085905330187</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6207</v>
+        <v>6263</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>雷科</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>668.7411345601663</v>
+        <v>765.2720069333697</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>137.5</v>
+        <v>174.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>57.00998440972848</v>
+        <v>64.23320038602203</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>34.46369973127747</v>
+        <v>27.21792470205234</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.6491793104869344</v>
+        <v>1.749374879314433</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>1</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>1.268371942833607</v>
+        <v>2.09167650044774</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6214</v>
+        <v>6292</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>精誠</t>
+          <t>迅德</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>667.2949289676344</v>
+        <v>764.9988665830756</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>193</v>
+        <v>69.3</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>69.93755588706904</v>
+        <v>58.82769337980037</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>25.86644929917606</v>
+        <v>35.086263712983</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.8410114262911069</v>
+        <v>0.969764113059612</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.8278529740297227</v>
+        <v>-0.0580874099300612</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6263</v>
+        <v>6245</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>立端</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>650.2720069333698</v>
+        <v>764.747742065145</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>174.5</v>
+        <v>87.5</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,49 +2195,49 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>64.23320040047527</v>
+        <v>55.92379901787831</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>27.21792470205233</v>
+        <v>32.31174727327967</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.749374879314433</v>
+        <v>0.8679182513210498</v>
       </c>
       <c r="K33" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L33" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L33" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M33" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>2.091676500928432</v>
+        <v>0.0261021472723608</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6236</v>
+        <v>6190</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>中湛</t>
+          <t>萬泰科</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>640.9052430491761</v>
+        <v>763.4401082803804</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>15.2</v>
+        <v>75.7</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>57.36238456757349</v>
+        <v>64.04600025898107</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>15.22872379289231</v>
+        <v>24.71851764494388</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.88139244812337</v>
+        <v>0.6145433098409944</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.9446727655490156</v>
+        <v>0.7989949934567258</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6174</v>
+        <v>6419</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>安碁</t>
+          <t>京晨科</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>636.3459815560723</v>
+        <v>722.0540442291181</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>61.1</v>
+        <v>167</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>67.29823083024623</v>
+        <v>59.15720278371422</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>26.42163661900609</v>
+        <v>20.6088526697419</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>2.81367713002037</v>
+        <v>0.7472543326540549</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>1.845493992536975</v>
+        <v>1.28863975184074</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6227</v>
+        <v>6194</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>茂綸</t>
+          <t>育富</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>632.6694892449791</v>
+        <v>716.0372177205978</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>132</v>
+        <v>32.4</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>50.79635545626021</v>
+        <v>76.32064807418226</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>40.99705766664707</v>
+        <v>28.53075287289798</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.26340331143039</v>
+        <v>1.203721772059782</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.3372599226739421</v>
+        <v>0.2468401552248352</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6209</v>
+        <v>6170</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>今國光</t>
+          <t>統振</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>629.1619990532332</v>
+        <v>702.5933745928497</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>89.09999999999999</v>
+        <v>49.5</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>65.14338002017902</v>
+        <v>62.49525431440698</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>38.05898587250088</v>
+        <v>22.14025782067861</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>2.321554534122129</v>
+        <v>1.228240082006089</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,48 +2425,48 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.8651085906171292</v>
+        <v>0.1034526724439336</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6173</v>
+        <v>6168</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>宏齊</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>615.0404335329927</v>
+        <v>685.5746933678303</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>284</v>
+        <v>39</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G38" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>51.81417152994361</v>
+        <v>52.47142057220758</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>38.46113759337639</v>
+        <v>50.08428720266225</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.2894454963500344</v>
+        <v>0.5560884894851494</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-4.757904489102373</v>
+        <v>-0.704758321552843</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6196</v>
+        <v>6205</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>詮欣</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>614.4620654083432</v>
+        <v>683.7986580112243</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>657</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>69.08420702545168</v>
+        <v>55.43677584185846</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>37.07741841217807</v>
+        <v>32.24196194640194</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.033563799544327</v>
+        <v>0.2314463443453805</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>11.1713856159794</v>
+        <v>0.07845814750976959</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6226</v>
+        <v>6233</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>光鼎</t>
+          <t>旺玖</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>612.1355245166013</v>
+        <v>671.7260991994888</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>43.55</v>
+        <v>25.15</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>59.44987755964361</v>
+        <v>81.46445771113447</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>48.7636480215823</v>
+        <v>38.86081688598598</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.6919680097510346</v>
+        <v>1.272609919948879</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.655855093195771</v>
+        <v>0.4283250190315876</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6456</v>
+        <v>6207</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>GIS-KY</t>
+          <t>雷科</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>605.540648217016</v>
+        <v>668.7411345601663</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>102</v>
+        <v>137.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>74.82551486864263</v>
+        <v>57.00998436644188</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>40.0254572582766</v>
+        <v>34.46369968441233</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.354064821701602</v>
+        <v>0.6491793104869344</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>2.372590979457123</v>
+        <v>1.268371944035319</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6190</v>
+        <v>6415</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>萬泰科</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>593.4401082803857</v>
+        <v>666.7161951852715</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>75.7</v>
+        <v>440</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,49 +2672,49 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>64.04600027803937</v>
+        <v>52.40766957922665</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>24.71851766249294</v>
+        <v>15.80260392447499</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.6145433098409944</v>
+        <v>1.424424167241902</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M42" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.7989949936009326</v>
+        <v>5.071526513372134</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6290</v>
+        <v>6236</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>良維</t>
+          <t>中湛</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>586.6597675168335</v>
+        <v>640.9052430491761</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>275.5</v>
+        <v>15.2</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>53.91596436909651</v>
+        <v>57.36238456757349</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>31.48982328622754</v>
+        <v>15.22872382883617</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.585349779624852</v>
+        <v>1.88139244812337</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.7769393464268486</v>
+        <v>-0.9446727653687568</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6239</v>
+        <v>6227</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>茂綸</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>585.3781409379224</v>
+        <v>632.6694892449791</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>304.5</v>
+        <v>132</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>58.99462996290797</v>
+        <v>50.7963554150602</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>18.75627048237731</v>
+        <v>40.99705764989073</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.8574705394532293</v>
+        <v>1.26340331143039</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>2.080020982920265</v>
+        <v>-0.3372599226979833</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6175</v>
+        <v>6164</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>立敦</t>
+          <t>華興</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>575.6090932699365</v>
+        <v>631.7559610066862</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>76.8</v>
+        <v>12.85</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>58.79523752187742</v>
+        <v>56.15465824046159</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>21.80273931447765</v>
+        <v>33.15465568588434</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.6949741971121548</v>
+        <v>0.5076778967976389</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>1.068429233021271</v>
+        <v>0.0956035093484659</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6198</v>
+        <v>6449</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>瑞築</t>
+          <t>鈺邦</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>565.0727307792552</v>
+        <v>621.5267894841497</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>19.9</v>
+        <v>265.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>52.85699818546281</v>
+        <v>66.48983496438817</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>8.112846492402799</v>
+        <v>20.89092372683939</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>2.375780077415277</v>
+        <v>1.452678948414975</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,48 +2902,48 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.1806396440745579</v>
+        <v>7.181762291537109</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6419</v>
+        <v>6173</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>京晨科</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>552.0540442291181</v>
+        <v>615.0404335329927</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>167</v>
+        <v>284</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G47" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>59.15720279646715</v>
+        <v>51.81417152122676</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>20.60885266392152</v>
+        <v>38.46113757511654</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.7472543326540549</v>
+        <v>0.2894454963500344</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>1.288639751600396</v>
+        <v>-4.757904489102373</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6218</v>
+        <v>6226</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>豪勉</t>
+          <t>光鼎</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>546.8911597592432</v>
+        <v>612.1355245166013</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>52.4</v>
+        <v>43.55</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>47.20474410438975</v>
+        <v>59.44987755834628</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>40.91543890380658</v>
+        <v>48.76364799204579</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.4881116075846632</v>
+        <v>0.6919680097510346</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>1</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-1.471798559567771</v>
+        <v>-0.6558550932053926</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6194</v>
+        <v>6414</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>育富</t>
+          <t>樺漢</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>546.0372177205978</v>
+        <v>602.0982470045204</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>32.4</v>
+        <v>404.5</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,49 +3043,49 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>76.32064812596651</v>
+        <v>57.11738243564334</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>28.5307528608276</v>
+        <v>18.042097774886</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.203721772059782</v>
+        <v>0.7815464571259116</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M49" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.2468401552488686</v>
+        <v>3.565346300213168</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6259</v>
+        <v>6290</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>百徽</t>
+          <t>良維</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>523.0461579925081</v>
+        <v>586.6597675168333</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>32.4</v>
+        <v>275.5</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>60.0349959358004</v>
+        <v>53.91596436909651</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>21.37912968974565</v>
+        <v>31.48982328622755</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.5445724812528652</v>
+        <v>1.585349779624852</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.4199459728842281</v>
+        <v>-0.7769393472680726</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6426</v>
+        <v>6239</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>統新</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>516.8526066800162</v>
+        <v>585.3781409379224</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>333.5</v>
+        <v>304.5</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>52.194678929756</v>
+        <v>58.99462994510788</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>36.1117760346272</v>
+        <v>18.75627049464003</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.4123370774568032</v>
+        <v>0.8574705394532293</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-7.136397404649752</v>
+        <v>2.08002098243953</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6164</v>
+        <v>6175</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>華興</t>
+          <t>立敦</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>516.7559610066862</v>
+        <v>575.609093269925</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>12.85</v>
+        <v>76.8</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>56.1546582810449</v>
+        <v>58.79523749974258</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>33.15465568588434</v>
+        <v>21.80273932422493</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.5076778967976389</v>
+        <v>0.6949741971121548</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.09560350936048161</v>
+        <v>1.06842923274487</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6182</v>
+        <v>6198</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>合晶</t>
+          <t>瑞築</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>514.2161891528026</v>
+        <v>565.0727307792552</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>124</v>
+        <v>19.9</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>52.94882989714019</v>
+        <v>52.85699818784091</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>25.74255175512646</v>
+        <v>8.112846515069716</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.4189462418028511</v>
+        <v>2.375780077415277</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.62307354990027</v>
+        <v>0.1806396440745579</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6166</v>
+        <v>6218</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>凌華</t>
+          <t>豪勉</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>512.2112904099923</v>
+        <v>546.8911597592432</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>120.5</v>
+        <v>52.4</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>44.60976875709057</v>
+        <v>47.2047440858761</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>24.8415823113362</v>
+        <v>40.91543888065162</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.8053223515701063</v>
+        <v>0.4881116075846632</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.009984162294639901</v>
+        <v>-1.471798559567771</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6233</v>
+        <v>6426</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>旺玖</t>
+          <t>統新</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>501.7260991994888</v>
+        <v>536.8526066800162</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>25.15</v>
+        <v>333.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>81.46445777236974</v>
+        <v>52.19467893352192</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>38.86081687470502</v>
+        <v>36.11177596802298</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.272609919948879</v>
+        <v>0.4123370774568032</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.4283250190676377</v>
+        <v>-7.136397404817981</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6279</v>
+        <v>6189</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>胡連</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>491.9470304660892</v>
+        <v>523.6467143828997</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>116.5</v>
+        <v>49.4</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,49 +3414,49 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>52.71840364229282</v>
+        <v>56.06364621641901</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>29.01466393917641</v>
+        <v>22.7947530739002</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.8189036046414141</v>
+        <v>0.7836196292095661</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.8686570803236604</v>
+        <v>0.07096347354475981</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6270</v>
+        <v>6259</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>倍微</t>
+          <t>百徽</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>479.1134308701738</v>
+        <v>523.0461579925081</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>30</v>
+        <v>32.4</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>52.7841788532775</v>
+        <v>60.03499583467376</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>22.27549661044465</v>
+        <v>21.37912963824856</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.8797534739302325</v>
+        <v>0.5445724812528652</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.07994182251468319</v>
+        <v>0.4199459730284365</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6414</v>
+        <v>6182</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>樺漢</t>
+          <t>合晶</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>477.0982470045205</v>
+        <v>514.2161891528026</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>404.5</v>
+        <v>124</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>57.11738253620604</v>
+        <v>52.94882988790624</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>18.04209769142399</v>
+        <v>25.74255179323526</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.7815464571259116</v>
+        <v>0.4189462418028511</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>3.565346298050032</v>
+        <v>0.6230735498762474</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6224</v>
+        <v>6166</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>聚鼎</t>
+          <t>凌華</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>473.1999644477357</v>
+        <v>512.2112904099923</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>75.59999999999999</v>
+        <v>120.5</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>41.98004456861032</v>
+        <v>44.60976869605839</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>27.89952621010353</v>
+        <v>24.84158231266657</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.6348181955619316</v>
+        <v>0.8053223515701063</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-1.331666631756278</v>
+        <v>0.0099841618620204</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6472</v>
+        <v>6442</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>保瑞</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>466.1965574734642</v>
+        <v>511.7117028513648</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>422.5</v>
+        <v>1725</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,49 +3626,49 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>50.41992218206427</v>
+        <v>56.9788275151882</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>29.70935161119055</v>
+        <v>21.83605841177992</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.099868495841427</v>
+        <v>1.280351027379353</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.081351652723399</v>
+        <v>23.62220533987413</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6228</v>
+        <v>6446</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>全譜</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>460.97482920335</v>
+        <v>494.2628339761211</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>18.2</v>
+        <v>1185</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,49 +3679,49 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>55.47875988693079</v>
+        <v>44.01936532435203</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>14.46788823211668</v>
+        <v>14.50517155868028</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.8027512262315833</v>
+        <v>0.358861899923304</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M61" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.6237254926246507</v>
+        <v>5.370355047993016</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6291</v>
+        <v>6163</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>沛亨</t>
+          <t>華電網</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>460.9077581619683</v>
+        <v>492.6162953794978</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>431</v>
+        <v>43.35</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>40.46159334517855</v>
+        <v>57.08437774730031</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>23.53305577153447</v>
+        <v>18.52534481590242</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.3196789457011434</v>
+        <v>0.7309014038778014</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-10.14872255222508</v>
+        <v>0.3060736693227449</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6284</v>
+        <v>6279</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>佳邦</t>
+          <t>胡連</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>459.3807198325165</v>
+        <v>491.9470304660892</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>78.59999999999999</v>
+        <v>116.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>51.86992015739667</v>
+        <v>52.71840361096825</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>17.75994591263262</v>
+        <v>29.01466397514623</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.7161866018108098</v>
+        <v>0.8189036046414141</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.4279065130189795</v>
+        <v>0.868657080203497</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6202</v>
+        <v>6270</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>盛群</t>
+          <t>倍微</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>453.001358619708</v>
+        <v>479.1134308701738</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>48.05972623831326</v>
+        <v>52.78417874404141</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>17.47406650801806</v>
+        <v>22.27549659826615</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.6985023402894067</v>
+        <v>0.8797534739302325</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.1456562213318584</v>
+        <v>0.0799418225627557</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6423</v>
+        <v>6224</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>億而得-創</t>
+          <t>聚鼎</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>450.1863567615816</v>
+        <v>473.1999644477357</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>86.90000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>52.54769807993029</v>
+        <v>41.98004445915609</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>25.05107878585363</v>
+        <v>27.89952613223418</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.2742533285901494</v>
+        <v>0.6348181955619316</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.1705821574398784</v>
+        <v>-1.331666631191476</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6189</v>
+        <v>6472</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>保瑞</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>448.6467143829002</v>
+        <v>466.1965574734645</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>49.4</v>
+        <v>422.5</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>56.06364627106888</v>
+        <v>50.41992198789773</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>22.79475309472368</v>
+        <v>29.70935163858232</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.7836196292095661</v>
+        <v>1.099868495841427</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.0709634736889735</v>
+        <v>-0.0813516536847718</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6465</v>
+        <v>6228</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>威潤</t>
+          <t>全譜</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>443.986618758881</v>
+        <v>460.9748292033502</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>42.3</v>
+        <v>18.2</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>45.86315048748587</v>
+        <v>55.47875985047104</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>9.183761447183906</v>
+        <v>14.4678883407912</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.748963486407009</v>
+        <v>0.8027512262315833</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.256049647342436</v>
+        <v>0.6237254928890303</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6415</v>
+        <v>6291</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>沛亨</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>436.7161951852718</v>
+        <v>460.9077581619683</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>52.40766970205978</v>
+        <v>40.4615933236335</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>15.80260390955954</v>
+        <v>23.53305587358149</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.424424167241902</v>
+        <v>0.3196789457011434</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>5.071526513251957</v>
+        <v>-10.14872255402768</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6449</v>
+        <v>6284</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>鈺邦</t>
+          <t>佳邦</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>421.5267894841497</v>
+        <v>459.3807198325165</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>265.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>66.48983490502724</v>
+        <v>51.869920139424</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>20.89092371889607</v>
+        <v>17.75994588055527</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.452678948414975</v>
+        <v>0.7161866018108098</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>7.181762291176605</v>
+        <v>0.4279065129228261</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6418</v>
+        <v>6423</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>詠昇</t>
+          <t>億而得-創</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>420.700976987964</v>
+        <v>450.1863567615816</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>33.75</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>44.89235794959576</v>
+        <v>52.5476979983064</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>29.73409736004325</v>
+        <v>25.05107885331422</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.832595890298992</v>
+        <v>0.2742533285901494</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.1709689177259676</v>
+        <v>-0.1705821574639285</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6266</v>
+        <v>6465</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>泰詠</t>
+          <t>威潤</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>408.1471130833605</v>
+        <v>443.9866187588811</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>25.5</v>
+        <v>42.3</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>50.60508501650214</v>
+        <v>45.86315047169001</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>17.45919190333844</v>
+        <v>9.183761858623187</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.539180343614801</v>
+        <v>1.748963486407009</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.0992084389847657</v>
+        <v>0.2560496471982683</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6443</v>
+        <v>6202</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>元晶</t>
+          <t>盛群</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>397.4990012354936</v>
+        <v>443.001358619708</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>26.55</v>
+        <v>58</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>48.48382188735862</v>
+        <v>48.05972621066464</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>28.18981749740771</v>
+        <v>17.47406647826123</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.3938788127899188</v>
+        <v>0.6985023402894067</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.0209382257847597</v>
+        <v>0.1456562213198379</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6451</v>
+        <v>6418</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>詠昇</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>395.6524387393775</v>
+        <v>420.700976987964</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>414</v>
+        <v>33.75</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>45.84248673444164</v>
+        <v>44.89235788282905</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>7.106288318524976</v>
+        <v>29.7340973836885</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.5000925253075035</v>
+        <v>1.832595890298992</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.31031757651043</v>
+        <v>-0.1709689181465732</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6229</v>
+        <v>6281</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>研通</t>
+          <t>全國電</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>395.0247747487821</v>
+        <v>413.672244936471</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>23.9</v>
+        <v>51</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>51.39141302398425</v>
+        <v>47.00197664977546</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>20.55547809035692</v>
+        <v>9.458771686832108</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.428930013135002</v>
+        <v>1.317498618504733</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.0325019729997909</v>
+        <v>0.0092318209110872</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6281</v>
+        <v>6230</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>全國電</t>
+          <t>尼得科超眾</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>393.6722449364258</v>
+        <v>412.1945016414793</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>51</v>
+        <v>113.5</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>47.00197664977546</v>
+        <v>53.14820793357584</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>9.458771680089436</v>
+        <v>19.1093839226581</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.317498618504733</v>
+        <v>0.3814862993822125</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.009231820935121799</v>
+        <v>0.3579122480760426</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6442</v>
+        <v>6266</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>泰詠</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>381.7117028513646</v>
+        <v>408.1471130833605</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>1725</v>
+        <v>25.5</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>56.97882750811538</v>
+        <v>50.60508498335416</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>21.83605846956664</v>
+        <v>17.45919186164242</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.280351027379353</v>
+        <v>1.539180343614801</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>23.62220534708434</v>
+        <v>0.0992084389487155</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6265</v>
+        <v>6443</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>方土昶</t>
+          <t>元晶</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>378.5608155093827</v>
+        <v>397.4990012354936</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>47.5</v>
+        <v>26.55</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>39.67810233328356</v>
+        <v>48.483821860554</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>17.04804770302811</v>
+        <v>28.18981753425761</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.333189530755283</v>
+        <v>0.3938788127899188</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.167984296615463</v>
+        <v>0.0209382257847597</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6432</v>
+        <v>6451</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>今展科</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>376.8995084473727</v>
+        <v>395.6524387393775</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>64.59999999999999</v>
+        <v>414</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>53.17920980947117</v>
+        <v>45.84248670178093</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>26.39869806109252</v>
+        <v>7.106288317613766</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.4042495147788498</v>
+        <v>0.5000925253075035</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.8996143497764603</v>
+        <v>0.3103175761498686</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6183</v>
+        <v>6229</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>關貿</t>
+          <t>研通</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>376.1222686059856</v>
+        <v>395.0247747487821</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>91.5</v>
+        <v>23.9</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>48.77875673690446</v>
+        <v>51.39141286093146</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>8.243397236339545</v>
+        <v>20.55547800280813</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.589554139097608</v>
+        <v>1.428930013135002</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.0438196033345073</v>
+        <v>0.0325019729997909</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6441</v>
+        <v>6265</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>廣錠</t>
+          <t>方土昶</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>369.7540345078644</v>
+        <v>378.5608155093827</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>21.95</v>
+        <v>47.5</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>40.29531753310158</v>
+        <v>39.67810231060563</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>16.11269726144111</v>
+        <v>17.04804765715081</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.1615442941299827</v>
+        <v>1.333189530755283</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.3881049775140242</v>
+        <v>0.1679842966274869</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6208</v>
+        <v>6432</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>日揚</t>
+          <t>今展科</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>359.4577548605457</v>
+        <v>376.8995084473727</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>77.2</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>47.83576581956694</v>
+        <v>53.17920978994192</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>17.2052795918907</v>
+        <v>26.39869806109251</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.8002707001062564</v>
+        <v>0.4042495147788498</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.5502032018445252</v>
+        <v>0.899614349812512</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6163</v>
+        <v>6183</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>華電網</t>
+          <t>關貿</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>352.6162953795008</v>
+        <v>376.1222686059856</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>43.35</v>
+        <v>91.5</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>57.08437776548262</v>
+        <v>48.77875679171267</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>18.52534474919032</v>
+        <v>8.243397236339545</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.7309014038778014</v>
+        <v>1.589554139097608</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.3060736693467807</v>
+        <v>0.0438196030941619</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6216</v>
+        <v>6441</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>居易</t>
+          <t>廣錠</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>343.5633575750132</v>
+        <v>369.7540345078644</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>19.85</v>
+        <v>21.95</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>45.89297478236784</v>
+        <v>40.29531757545998</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>34.69691238229354</v>
+        <v>16.11269730904645</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1.864037545393238</v>
+        <v>0.1615442941299827</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.1670186168997396</v>
+        <v>-0.3881049776462163</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6462</v>
+        <v>6208</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>神盾</t>
+          <t>日揚</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>341.3738673679572</v>
+        <v>359.4577548605457</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>100</v>
+        <v>77.2</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>47.07322865420961</v>
+        <v>47.83576579274791</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>19.30752207057915</v>
+        <v>17.20527966669469</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.4270397174632107</v>
+        <v>0.8002707001062564</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.0476345002211124</v>
+        <v>0.5502032014839991</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6275</v>
+        <v>6216</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>元山</t>
+          <t>居易</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>340.4507164561119</v>
+        <v>343.5633575750132</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>45.7</v>
+        <v>19.85</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>46.67910374636458</v>
+        <v>45.89297476220624</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>32.95716408155437</v>
+        <v>34.69691242629125</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.338404458329924</v>
+        <v>1.864037545393238</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.0261489378144913</v>
+        <v>0.1670186169237747</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6165</v>
+        <v>6462</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>浪凡</t>
+          <t>神盾</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>329.9390659049413</v>
+        <v>341.3738673679571</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>48.6</v>
+        <v>100</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>49.69662828360613</v>
+        <v>47.07322867492884</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>13.87683298251701</v>
+        <v>19.30752205672641</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.3441976761086278</v>
+        <v>0.4270397174632107</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.1008783831147843</v>
+        <v>-0.0476345008219687</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6435</v>
+        <v>6275</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>大中</t>
+          <t>元山</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>328.0819099393105</v>
+        <v>340.450716456112</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>254.5</v>
+        <v>45.7</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>49.32711977619955</v>
+        <v>46.67910369452083</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>16.43343094509335</v>
+        <v>32.95716408498367</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.403437962390579</v>
+        <v>1.338404458329924</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,48 +5075,48 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>1.254124118102448</v>
+        <v>-0.0261489379106359</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6167</v>
+        <v>6165</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>久正</t>
+          <t>浪凡</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>323.4744112284328</v>
+        <v>329.9390659049413</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>10.3</v>
+        <v>48.6</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="G88" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>48.77258351304166</v>
+        <v>49.69662825138398</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>14.02569956253096</v>
+        <v>13.87683300745085</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.9922289282288724</v>
+        <v>0.3441976761086278</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>1</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.0238215499564229</v>
+        <v>-0.1008783833070644</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6474</v>
+        <v>6435</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>華豫寧</t>
+          <t>大中</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>320.6925120352101</v>
+        <v>328.0819099393108</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>35.45</v>
+        <v>254.5</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>41.10006108390709</v>
+        <v>49.32711978143758</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>14.77511931403028</v>
+        <v>16.4334310504963</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.5706794349438421</v>
+        <v>0.403437962390579</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.0911774075664456</v>
+        <v>1.254124117645802</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6409</v>
+        <v>6276</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>旭隼</t>
+          <t>安鈦克</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>320.0670968046075</v>
+        <v>325.0885263851857</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>875</v>
+        <v>19.4</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>40.1676559816662</v>
+        <v>51.13980486401622</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>13.08632964351881</v>
+        <v>15.17360925715705</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.6640174757136786</v>
+        <v>2.146836217221783</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>2.678435637788709</v>
+        <v>0.1823471192524018</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>volume_break, market_above_ma60, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6417</v>
+        <v>6409</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>韋僑</t>
+          <t>旭隼</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>312.2017539264371</v>
+        <v>324.6941829084438</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>105.5</v>
+        <v>875</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,66 +5269,66 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>52.42420247890689</v>
+        <v>40.16765605842159</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>31.254420242606</v>
+        <v>13.08632973201268</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.7440867915557611</v>
+        <v>1.022451931402703</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.6808835119746339</v>
+        <v>2.678435629376573</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6237</v>
+        <v>6167</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>驊訊</t>
+          <t>久正</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>306.8236557533665</v>
+        <v>323.4744112284328</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>33.85</v>
+        <v>10.3</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G92" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>42.55698144235106</v>
+        <v>48.77258351304166</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>23.08373664140991</v>
+        <v>14.02569958205226</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.448135881669552</v>
+        <v>0.9922289282288724</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>1</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.1226810895435605</v>
+        <v>0.0238215498526453</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6222</v>
+        <v>6474</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>立軒</t>
+          <t>華豫寧</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>305.6634335173167</v>
+        <v>320.6925120352101</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>20.1</v>
+        <v>35.45</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>52.39779276827882</v>
+        <v>41.10006096478962</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>7.296341453277932</v>
+        <v>14.77511923356459</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.6093789514416382</v>
+        <v>0.5706794349438421</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.3592621557702961</v>
+        <v>0.09117740766258529</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6230</v>
+        <v>6417</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>尼得科超眾</t>
+          <t>韋僑</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>297.1945016414768</v>
+        <v>312.2017539264372</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>113.5</v>
+        <v>105.5</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>53.14820806093948</v>
+        <v>52.4242024449299</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>19.10938387627882</v>
+        <v>31.25442019872245</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.3814862993822125</v>
+        <v>0.7440867915557611</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.3579122491576063</v>
+        <v>0.6808835119746339</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6220</v>
+        <v>6237</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>岳豐</t>
+          <t>驊訊</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>290.5874887812593</v>
+        <v>306.823655753364</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>25.35</v>
+        <v>33.85</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>44.42716441399831</v>
+        <v>42.55698135074841</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>16.09477701374473</v>
+        <v>23.08373662666472</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.8105369556031405</v>
+        <v>1.448135881669552</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>1</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.0935537644292259</v>
+        <v>-0.1226810898199542</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6243</v>
+        <v>6222</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>迅杰</t>
+          <t>立軒</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>289.5419409872806</v>
+        <v>305.6634335173167</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>38</v>
+        <v>20.1</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>43.52474553034185</v>
+        <v>52.39779272878874</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>14.09458918036418</v>
+        <v>7.296341535901033</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.4161645248904377</v>
+        <v>0.6093789514416382</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.1196448866047484</v>
+        <v>0.359262155938538</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6405</v>
+        <v>6220</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>悅城</t>
+          <t>岳豐</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>282.3061191124186</v>
+        <v>290.5874887812593</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>40.85</v>
+        <v>25.35</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>48.60224923511461</v>
+        <v>44.42716450306976</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>17.67541354206529</v>
+        <v>16.09477701374472</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.6306119112418593</v>
+        <v>0.8105369556031405</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.2641791516001224</v>
+        <v>0.0935537643931743</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6184</v>
+        <v>6243</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>大豐電</t>
+          <t>迅杰</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>272.8047530740918</v>
+        <v>289.5419409872806</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>41.76788383077786</v>
+        <v>43.52474542330941</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>24.66786619301122</v>
+        <v>14.09458919318579</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.3870034415231174</v>
+        <v>0.4161645248904377</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,11 +5658,11 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.0495415442012102</v>
+        <v>0.1196448866408061</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -5679,7 +5679,7 @@
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>268.0427765139507</v>
+        <v>288.0427765139507</v>
       </c>
       <c r="E99" s="2" t="n">
         <v>136.5</v>
@@ -5693,7 +5693,7 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>47.85730916320245</v>
+        <v>47.85730913709202</v>
       </c>
       <c r="I99" s="2" t="n">
         <v>13.89664647254133</v>
@@ -5702,16 +5702,16 @@
         <v>0.8836082477600172</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L99" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M99" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.5330341817595637</v>
+        <v>-0.5330341818797086</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -5721,21 +5721,21 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6446</v>
+        <v>6405</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>悅城</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>264.2628339761211</v>
+        <v>282.3061191124186</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>1185</v>
+        <v>40.85</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>44.01936530881039</v>
+        <v>48.60224923294825</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>14.50517148582951</v>
+        <v>17.67541353472171</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.358861899923304</v>
+        <v>0.6306119112418593</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>5.370355049194885</v>
+        <v>-0.2641791515881028</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6464</v>
+        <v>6184</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>台數科</t>
+          <t>大豐電</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>258.3929120730878</v>
+        <v>272.8047530740918</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>76.3</v>
+        <v>40</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>44.62086219667224</v>
+        <v>41.76788341199077</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>22.72793336656546</v>
+        <v>24.66786619811168</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.5487125439648438</v>
+        <v>0.3870034415231174</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.0511957431075392</v>
+        <v>0.0495415442973559</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6215</v>
+        <v>6283</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>和椿</t>
+          <t>淳安</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>257.4570631655784</v>
+        <v>265.004016569531</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>94.09999999999999</v>
+        <v>18.55</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>39.28521573822808</v>
+        <v>38.82216399552047</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>10.02424909779684</v>
+        <v>16.08321364036515</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.6188861190602412</v>
+        <v>0.9922855921503912</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.2979045504368792</v>
+        <v>0.0415705595050144</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6412</v>
+        <v>6464</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>群電</t>
+          <t>台數科</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>255.6217502706922</v>
+        <v>258.3929120730878</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>73.3</v>
+        <v>76.3</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>35.16948240620714</v>
+        <v>44.62086209957697</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>18.42672828777632</v>
+        <v>22.72793339952625</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.002946138312441</v>
+        <v>0.5487125439648438</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.0942360015473245</v>
+        <v>-0.0511957430354371</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6177</v>
+        <v>6215</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>達麗</t>
+          <t>和椿</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>246.5192584514701</v>
+        <v>257.4570631655783</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>46.6</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>48.89539790795261</v>
+        <v>39.28521542696505</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>12.85339731377523</v>
+        <v>10.02424915908419</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.7005920717808376</v>
+        <v>0.6188861190602412</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.0387185611466178</v>
+        <v>-0.297904551999105</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6269</v>
+        <v>6412</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>台郡</t>
+          <t>群電</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>244.9417086932867</v>
+        <v>255.6217502706922</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>63.5</v>
+        <v>73.3</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,49 +6011,49 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>44.80628807862051</v>
+        <v>35.1694824970523</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>11.43929208318473</v>
+        <v>18.42672819067131</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.4129567304469763</v>
+        <v>1.002946138312441</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L105" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M105" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.1913302536686187</v>
+        <v>0.09423600130697821</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6246</v>
+        <v>6176</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>臺龍</t>
+          <t>瑞儀</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>208.1191454439394</v>
+        <v>249.8213941763336</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>12.5</v>
+        <v>90.5</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,49 +6064,49 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>42.8933447374504</v>
+        <v>46.91766715153125</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>18.82470330326492</v>
+        <v>11.73595885106663</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.2537615279397819</v>
+        <v>0.5197740068897783</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L106" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M106" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.0272659604668555</v>
+        <v>-0.2900353925131635</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, dealer_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6203</v>
+        <v>6177</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>海韻電</t>
+          <t>達麗</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>201.0080651735346</v>
+        <v>246.5192584514701</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>59.8</v>
+        <v>46.6</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>44.80527123066266</v>
+        <v>48.89539785240141</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>8.889687184309794</v>
+        <v>12.85339740440257</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.8566279569326398</v>
+        <v>0.7005920717808376</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.0805218722884779</v>
+        <v>-0.038718561182671</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6244</v>
+        <v>6269</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>茂迪</t>
+          <t>台郡</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>181.6697420999223</v>
+        <v>229.9417086932867</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>22.1</v>
+        <v>63.5</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>39.65904038334173</v>
+        <v>44.80628810126909</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>16.21589170670196</v>
+        <v>11.4392920785138</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.6168371692503486</v>
+        <v>0.4129567304469763</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.09385232589758941</v>
+        <v>-0.1913302541252735</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6176</v>
+        <v>6246</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>瑞儀</t>
+          <t>臺龍</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>174.8213941763336</v>
+        <v>208.1191454439405</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>90.5</v>
+        <v>12.5</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>46.91766698143552</v>
+        <v>42.89334406306943</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>11.73595884963725</v>
+        <v>18.82470333709141</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.5197740068897783</v>
+        <v>0.2537615279397819</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.290035391277422</v>
+        <v>-0.0272659602505436</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6283</v>
+        <v>6203</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>淳安</t>
+          <t>海韻電</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>155.004016569531</v>
+        <v>201.0080651735347</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>18.55</v>
+        <v>59.8</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>38.8221638705047</v>
+        <v>44.80527094404214</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>16.08321370601751</v>
+        <v>8.889687145058632</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.9922855921503912</v>
+        <v>0.8566279569326398</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.0415705598535165</v>
+        <v>0.080521872360586</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6161</v>
+        <v>6244</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>捷波</t>
+          <t>茂迪</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>146.3145659345828</v>
+        <v>181.6697420999205</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>48.35</v>
+        <v>22.1</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>43.28278796260578</v>
+        <v>39.65904024306576</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>8.652911549000549</v>
+        <v>16.21589170884489</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.7872840598310938</v>
+        <v>0.6168371692503486</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.0181615214819931</v>
+        <v>-0.0938523258134679</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6411</v>
+        <v>6161</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>晶焱</t>
+          <t>捷波</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>146.2657379693424</v>
+        <v>146.3145659345828</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>76.40000000000001</v>
+        <v>48.35</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>40.21789242624138</v>
+        <v>43.28278793151101</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>7.970424429335111</v>
+        <v>8.652911525097791</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>1.45750944117738</v>
+        <v>0.7872840598310938</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.0394233404328921</v>
+        <v>-0.0181615215420811</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6276</v>
+        <v>6411</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>安鈦克</t>
+          <t>晶焱</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>125.0885263851856</v>
+        <v>146.2657379693425</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>19.4</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>51.13980488021112</v>
+        <v>40.21789239595231</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>15.17360924919999</v>
+        <v>7.970424450327878</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>2.146836217221783</v>
+        <v>1.45750944117738</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,11 +6453,11 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.1823471193485382</v>
+        <v>-0.0394233406732288</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>97.50627578849048</v>
+        <v>97.50627578849046</v>
       </c>
       <c r="E114" s="2" t="n">
         <v>24.5</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>40.37867812237103</v>
+        <v>40.37867803387088</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>19.46071089704546</v>
+        <v>19.46071090074099</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>1.221475528845163</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.1544547818619721</v>
+        <v>-0.1544547818379348</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>96.47131283197616</v>
+        <v>96.47131283197434</v>
       </c>
       <c r="E115" s="2" t="n">
         <v>36</v>
@@ -6541,10 +6541,10 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>32.76172170357147</v>
+        <v>32.76172176123416</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>17.03211254777749</v>
+        <v>17.03211250563939</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>0.6789805144527027</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.2963565068571383</v>
+        <v>-0.2963565071215137</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
